--- a/Personal-Management-Finance-Model/START-Personal-Budgeting-File_v2.xlsx
+++ b/Personal-Management-Finance-Model/START-Personal-Budgeting-File_v2.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Magic\OneDrive\Documents\GitHub\Financial-Analysis-Portfolio\Personal-Management-Finance-Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABF2C39-0A87-43BD-8EC7-0D2176843CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3363EDA7-3414-477D-BA6F-37FEC4F79B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
-    <sheet name="Inputs" sheetId="3" r:id="rId2"/>
+    <sheet name="Cover" sheetId="4" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Inputs" sheetId="3" r:id="rId3"/>
+    <sheet name="__tracelight_scratchpad__" sheetId="5" state="veryHidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="94">
   <si>
     <t>Personal Finance Tracker</t>
   </si>
@@ -239,6 +241,84 @@
   </si>
   <si>
     <t>New Shoes</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Inputs</t>
+  </si>
+  <si>
+    <t>Latest activity</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>mohamedeones123@gmail.com</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>+20 101 301 9563</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
+  </si>
+  <si>
+    <t>linkedin.com/in/mohamed-magdy-finance</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>github.com/Mohamed-Magdy-Finance</t>
+  </si>
+  <si>
+    <t>CONTACT</t>
+  </si>
+  <si>
+    <t>TOTAL INCOME</t>
+  </si>
+  <si>
+    <t>TOTAL EXPENSES</t>
+  </si>
+  <si>
+    <t>TOTAL SAVINGS</t>
+  </si>
+  <si>
+    <t>SAVINGS RATE</t>
+  </si>
+  <si>
+    <t>QUICK ACCESS</t>
+  </si>
+  <si>
+    <t>PERSONAL FINANCE TRACKER</t>
+  </si>
+  <si>
+    <t>Mohamed Magdy | FP&amp;A Analyst</t>
+  </si>
+  <si>
+    <t>Annual financial overview | Figures in USD</t>
+  </si>
+  <si>
+    <t>EXECUTIVE SUMMARY</t>
+  </si>
+  <si>
+    <t>Monthly insights</t>
+  </si>
+  <si>
+    <t>Maintain data</t>
+  </si>
+  <si>
+    <t>Clarity.</t>
+  </si>
+  <si>
+    <t>Control.</t>
+  </si>
+  <si>
+    <t>Insight.</t>
   </si>
 </sst>
 </file>
@@ -248,7 +328,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0_);\(#,##0\);\-\-_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -259,35 +339,41 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF293D68"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FF293D68"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -295,12 +381,14 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -308,23 +396,275 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0432FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFD9E2F3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFD9E2F3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFD9E2F3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFFFF99"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FFD9E2F3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFD9E2F3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF293D68"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,8 +689,38 @@
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF293D68"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -413,11 +783,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF293D68"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF293D68"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF293D68"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF293D68"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF293D68"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFFFF99"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9E2F3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9E2F3"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9E2F3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -472,13 +1160,488 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="19" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="16" fontId="27" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="38" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="14" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="30" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="42" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="43" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="39" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="39" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="31" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="34" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="41" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="41" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFC00000"/>
@@ -522,22 +1685,6 @@
     <dxf>
       <font>
         <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
       </font>
       <fill>
         <patternFill patternType="none"/>
@@ -1343,7 +2490,336 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="6">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{C6A975AE-8985-4526-A968-D41ADD903259}">
+  <we:reference id="wa200008399" version="1.0.0.5" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200008399" version="1.0.0.5" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="ProjectMetadata" value="&quot;{\&quot;projectId\&quot;:\&quot;508e72d0-5221-4888-ba17-7372b5e10090\&quot;}&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB89677-AC4B-4846-BA1B-FDEF40387B29}">
+  <sheetPr>
+    <tabColor rgb="FF293D68"/>
+  </sheetPr>
+  <dimension ref="B1:I22"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" style="7" customWidth="1"/>
+    <col min="2" max="2" width="16" style="7" customWidth="1"/>
+    <col min="3" max="9" width="14" style="7" customWidth="1"/>
+    <col min="10" max="16384" width="11.25" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+    </row>
+    <row r="3" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="166" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="166"/>
+      <c r="D3" s="166"/>
+      <c r="E3" s="166"/>
+      <c r="F3" s="166"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="166"/>
+      <c r="I3" s="166"/>
+    </row>
+    <row r="4" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="169" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+    </row>
+    <row r="5" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="170" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="171"/>
+    </row>
+    <row r="6" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+    </row>
+    <row r="7" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="172" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="172"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="172"/>
+      <c r="G7" s="172"/>
+      <c r="H7" s="172"/>
+      <c r="I7" s="172"/>
+    </row>
+    <row r="8" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="156" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="153"/>
+      <c r="D8" s="156" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="181"/>
+      <c r="F8" s="182" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="183"/>
+      <c r="H8" s="156" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="158"/>
+    </row>
+    <row r="9" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="44">
+        <f>Dashboard!P10</f>
+        <v>44691</v>
+      </c>
+      <c r="C9" s="130"/>
+      <c r="D9" s="44">
+        <f>Dashboard!P20</f>
+        <v>17865</v>
+      </c>
+      <c r="E9" s="130"/>
+      <c r="F9" s="184">
+        <f>Dashboard!P23</f>
+        <v>26826</v>
+      </c>
+      <c r="G9" s="174"/>
+      <c r="H9" s="49">
+        <f>IF(Dashboard!P10=0,0,Dashboard!P23/Dashboard!P10)</f>
+        <v>0.6002550849164261</v>
+      </c>
+      <c r="I9" s="159"/>
+    </row>
+    <row r="10" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="157"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="154"/>
+      <c r="F10" s="173"/>
+      <c r="G10" s="178"/>
+      <c r="H10" s="157"/>
+      <c r="I10" s="161"/>
+    </row>
+    <row r="11" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="128"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="128"/>
+      <c r="H11" s="128"/>
+      <c r="I11" s="128"/>
+    </row>
+    <row r="12" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="172" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="172"/>
+      <c r="D12" s="172"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="180"/>
+      <c r="H12" s="172"/>
+      <c r="I12" s="172"/>
+    </row>
+    <row r="13" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="46"/>
+    </row>
+    <row r="14" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="197" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="197" t="s">
+        <v>90</v>
+      </c>
+      <c r="F14" s="198"/>
+      <c r="G14" s="198"/>
+      <c r="H14" s="202">
+        <f>MAX(Inputs!B5:B95)</f>
+        <v>44806</v>
+      </c>
+      <c r="I14" s="203"/>
+    </row>
+    <row r="15" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="199"/>
+      <c r="C15" s="200"/>
+      <c r="D15" s="200"/>
+      <c r="E15" s="201"/>
+      <c r="F15" s="200"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="204"/>
+      <c r="I15" s="205"/>
+    </row>
+    <row r="16" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="147"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="128"/>
+      <c r="G16" s="147"/>
+      <c r="H16" s="168"/>
+      <c r="I16" s="128"/>
+    </row>
+    <row r="17" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="175" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="172"/>
+      <c r="D17" s="172"/>
+      <c r="E17" s="172"/>
+      <c r="F17" s="172"/>
+      <c r="G17" s="172"/>
+      <c r="H17" s="172"/>
+      <c r="I17" s="172"/>
+    </row>
+    <row r="18" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="189" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="195" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="190"/>
+      <c r="E18" s="190"/>
+      <c r="F18" s="189" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="195" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="190"/>
+      <c r="I18" s="191"/>
+    </row>
+    <row r="19" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="196" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="196" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="193"/>
+      <c r="I19" s="194"/>
+    </row>
+    <row r="20" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="128"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="128"/>
+      <c r="G20" s="147"/>
+      <c r="H20" s="128"/>
+      <c r="I20" s="128"/>
+    </row>
+    <row r="21" spans="2:9" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="176" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="177"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="176" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="176"/>
+      <c r="G21" s="177"/>
+      <c r="H21" s="176" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="176"/>
+    </row>
+    <row r="22" spans="2:9" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="128"/>
+      <c r="G22" s="128"/>
+      <c r="H22" s="128"/>
+      <c r="I22" s="128"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1" tooltip="Send email" display="mohamedeones123@gmail.com" xr:uid="{A7F417F8-4EA1-4AD9-8F09-6C59747C780F}"/>
+    <hyperlink ref="B17" r:id="rId2" tooltip="Open GitHub profile" display="github.com/Mohamed-Magdy-Finance" xr:uid="{FCE09E7A-C8F3-456D-95D3-8A02EF6EE26B}"/>
+    <hyperlink ref="B13" location="Dashboard!A1" tooltip="Open Dashboard" display="Dashboard" xr:uid="{08A49890-2A15-4471-BED4-B18D201ED66F}"/>
+    <hyperlink ref="E13" location="Inputs!A1" tooltip="Open Inputs" display="Inputs" xr:uid="{ACF47FB8-17A0-46DC-BBF0-88CDBE4612A4}"/>
+    <hyperlink ref="C18" r:id="rId3" tooltip="Send email" xr:uid="{C20CACD0-86D4-4D14-8E98-31DA105285DF}"/>
+    <hyperlink ref="G18" r:id="rId4" tooltip="Open LinkedIn profile" xr:uid="{07524C07-757B-4EC4-BB9A-2702AAC0F5C7}"/>
+    <hyperlink ref="C19" r:id="rId5" tooltip="Call phone" xr:uid="{FDDA7DFD-1FE6-46F0-AC91-127AD6F4FE80}"/>
+    <hyperlink ref="G19" r:id="rId6" tooltip="Open GitHub profile" xr:uid="{0863C5D7-8BDA-4DCA-853B-D2CB6C9D2CB8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1536,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="9">
-        <f t="shared" ref="P7:P10" si="0">SUM(C7:N7)</f>
+        <f t="shared" ref="P7:P9" si="0">SUM(C7:N7)</f>
         <v>12330</v>
       </c>
     </row>
@@ -1897,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" ref="P15:P20" si="3">SUM(C15:N15)</f>
+        <f t="shared" ref="P15:P19" si="3">SUM(C15:N15)</f>
         <v>1019</v>
       </c>
     </row>
@@ -2192,7 +3668,7 @@
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="15">
-        <f t="shared" ref="C21:N21" si="5">IF(D20=0,"",D20/C20-1)</f>
+        <f t="shared" ref="D21:N21" si="5">IF(D20=0,"",D20/C20-1)</f>
         <v>-0.28793486306439675</v>
       </c>
       <c r="E21" s="15">
@@ -2399,10 +3875,10 @@
       <c r="G27" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="33"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="30"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3421,7 +4897,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:H999"/>
   <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6046,4 +7522,922 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2A9847-8B0D-43E1-A16B-8D11C82E7ABD}">
+  <dimension ref="A1:H137"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="7"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="32" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="34"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="35"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="36"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="36"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="62"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="62"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="66"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="70"/>
+      <c r="B46" s="70"/>
+      <c r="C46" s="70"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="62"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="64"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="66"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="68"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="70"/>
+      <c r="B50" s="70"/>
+      <c r="C50" s="72"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="51"/>
+      <c r="B52" s="52"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="51"/>
+      <c r="B53" s="52"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="53"/>
+      <c r="B54" s="54"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="51"/>
+      <c r="B56" s="52"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="51"/>
+      <c r="B57" s="52"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="53"/>
+      <c r="B58" s="54"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="55"/>
+      <c r="B60" s="52"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="51"/>
+      <c r="B61" s="52"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="53"/>
+      <c r="B62" s="54"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="59"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="59"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="79"/>
+      <c r="B67" s="80"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="60"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="61"/>
+      <c r="B70" s="73"/>
+      <c r="C70" s="73"/>
+      <c r="D70" s="73"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="73"/>
+      <c r="G70" s="73"/>
+      <c r="H70" s="76"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="65"/>
+      <c r="B71" s="87"/>
+      <c r="C71" s="74"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="67"/>
+      <c r="F71" s="87"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="77"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="69"/>
+      <c r="B72" s="88"/>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="71"/>
+      <c r="F72" s="88"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="78"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="7"/>
+      <c r="H74" s="7"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="84"/>
+      <c r="B75" s="84"/>
+      <c r="C75" s="84"/>
+      <c r="D75" s="84"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="84"/>
+      <c r="G75" s="84"/>
+      <c r="H75" s="84"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="84"/>
+      <c r="B76" s="84"/>
+      <c r="C76" s="84"/>
+      <c r="D76" s="84"/>
+      <c r="E76" s="84"/>
+      <c r="F76" s="84"/>
+      <c r="G76" s="84"/>
+      <c r="H76" s="84"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="37"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="7"/>
+      <c r="H78" s="7"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="91"/>
+      <c r="B80" s="92"/>
+      <c r="C80" s="92"/>
+      <c r="D80" s="92"/>
+      <c r="E80" s="93"/>
+      <c r="F80" s="92"/>
+      <c r="G80" s="92"/>
+      <c r="H80" s="94"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="95"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="97"/>
+      <c r="F81" s="96"/>
+      <c r="G81" s="96"/>
+      <c r="H81" s="98"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="99"/>
+      <c r="B82" s="100"/>
+      <c r="C82" s="100"/>
+      <c r="D82" s="100"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="100"/>
+      <c r="G82" s="100"/>
+      <c r="H82" s="102"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="103"/>
+      <c r="B84" s="109"/>
+      <c r="C84" s="109"/>
+      <c r="D84" s="109"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="109"/>
+      <c r="G84" s="109"/>
+      <c r="H84" s="112"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="105"/>
+      <c r="B85" s="115"/>
+      <c r="C85" s="110"/>
+      <c r="D85" s="110"/>
+      <c r="E85" s="106"/>
+      <c r="F85" s="115"/>
+      <c r="G85" s="110"/>
+      <c r="H85" s="113"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="107"/>
+      <c r="B86" s="116"/>
+      <c r="C86" s="111"/>
+      <c r="D86" s="111"/>
+      <c r="E86" s="108"/>
+      <c r="F86" s="116"/>
+      <c r="G86" s="111"/>
+      <c r="H86" s="114"/>
+    </row>
+    <row r="88" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="56"/>
+      <c r="B88" s="32"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="57"/>
+      <c r="B89" s="34"/>
+      <c r="C89" s="34"/>
+      <c r="D89" s="34"/>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+      <c r="G89" s="34"/>
+      <c r="H89" s="34"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="58"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="35"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="35"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+    </row>
+    <row r="92" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="38"/>
+      <c r="B92" s="38"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="38"/>
+      <c r="F92" s="38"/>
+      <c r="G92" s="38"/>
+      <c r="H92" s="38"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="43"/>
+      <c r="B94" s="40"/>
+      <c r="C94" s="43"/>
+      <c r="D94" s="40"/>
+      <c r="E94" s="43"/>
+      <c r="F94" s="40"/>
+      <c r="G94" s="43"/>
+      <c r="H94" s="46"/>
+    </row>
+    <row r="95" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A95" s="44"/>
+      <c r="B95" s="41"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="44"/>
+      <c r="F95" s="41"/>
+      <c r="G95" s="49"/>
+      <c r="H95" s="47"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="45"/>
+      <c r="B96" s="42"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="42"/>
+      <c r="E96" s="45"/>
+      <c r="F96" s="42"/>
+      <c r="G96" s="45"/>
+      <c r="H96" s="48"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="7"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="7"/>
+      <c r="H98" s="7"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="50"/>
+      <c r="B99" s="50"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="50"/>
+      <c r="E99" s="50"/>
+      <c r="F99" s="39"/>
+      <c r="G99" s="50"/>
+      <c r="H99" s="50"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="89"/>
+      <c r="B100" s="46"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="89"/>
+      <c r="E100" s="46"/>
+      <c r="F100" s="7"/>
+      <c r="G100" s="43"/>
+      <c r="H100" s="46"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="79"/>
+      <c r="B101" s="80"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="79"/>
+      <c r="E101" s="80"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="83"/>
+      <c r="H101" s="80"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="79"/>
+      <c r="B102" s="80"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="79"/>
+      <c r="E102" s="80"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="86"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="81"/>
+      <c r="B103" s="82"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="81"/>
+      <c r="E103" s="82"/>
+      <c r="F103" s="7"/>
+      <c r="G103" s="81"/>
+      <c r="H103" s="82"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="90"/>
+      <c r="B104" s="90"/>
+      <c r="C104" s="90"/>
+      <c r="D104" s="90"/>
+      <c r="E104" s="90"/>
+      <c r="F104" s="90"/>
+      <c r="G104" s="90"/>
+      <c r="H104" s="90"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="117"/>
+      <c r="B105" s="118"/>
+      <c r="C105" s="118"/>
+      <c r="D105" s="118"/>
+      <c r="E105" s="119"/>
+      <c r="F105" s="118"/>
+      <c r="G105" s="118"/>
+      <c r="H105" s="120"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="121"/>
+      <c r="B106" s="122"/>
+      <c r="C106" s="123"/>
+      <c r="D106" s="123"/>
+      <c r="E106" s="124"/>
+      <c r="F106" s="122"/>
+      <c r="G106" s="123"/>
+      <c r="H106" s="125"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="107"/>
+      <c r="B107" s="126"/>
+      <c r="C107" s="111"/>
+      <c r="D107" s="111"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="126"/>
+      <c r="G107" s="111"/>
+      <c r="H107" s="114"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="37"/>
+      <c r="B108" s="37"/>
+      <c r="C108" s="37"/>
+      <c r="D108" s="37"/>
+      <c r="E108" s="37"/>
+      <c r="F108" s="37"/>
+      <c r="G108" s="37"/>
+      <c r="H108" s="37"/>
+    </row>
+    <row r="110" spans="1:8" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="146"/>
+      <c r="B110" s="146"/>
+      <c r="C110" s="146"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="127"/>
+      <c r="B112" s="127"/>
+      <c r="C112" s="127"/>
+      <c r="D112" s="128"/>
+      <c r="E112" s="128"/>
+      <c r="F112" s="128"/>
+      <c r="G112" s="128"/>
+      <c r="H112" s="128"/>
+    </row>
+    <row r="113" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A113" s="134"/>
+      <c r="B113" s="134"/>
+      <c r="C113" s="134"/>
+      <c r="D113" s="135"/>
+      <c r="E113" s="135"/>
+      <c r="F113" s="135"/>
+      <c r="G113" s="135"/>
+      <c r="H113" s="135"/>
+    </row>
+    <row r="114" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A114" s="134"/>
+      <c r="B114" s="134"/>
+      <c r="C114" s="134"/>
+      <c r="D114" s="128"/>
+      <c r="E114" s="128"/>
+      <c r="F114" s="128"/>
+      <c r="G114" s="128"/>
+      <c r="H114" s="128"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="127"/>
+      <c r="B115" s="127"/>
+      <c r="C115" s="127"/>
+      <c r="D115" s="136"/>
+      <c r="E115" s="136"/>
+      <c r="F115" s="136"/>
+      <c r="G115" s="137"/>
+      <c r="H115" s="138"/>
+    </row>
+    <row r="116" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="167"/>
+      <c r="B116" s="167"/>
+      <c r="C116" s="167"/>
+      <c r="D116" s="128"/>
+      <c r="E116" s="128"/>
+      <c r="F116" s="128"/>
+      <c r="G116" s="128"/>
+      <c r="H116" s="128"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="139"/>
+      <c r="B117" s="139"/>
+      <c r="C117" s="139"/>
+      <c r="D117" s="156"/>
+      <c r="E117" s="153"/>
+      <c r="F117" s="156"/>
+      <c r="G117" s="158"/>
+      <c r="H117" s="128"/>
+    </row>
+    <row r="118" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A118" s="127"/>
+      <c r="B118" s="127"/>
+      <c r="C118" s="127"/>
+      <c r="D118" s="44"/>
+      <c r="E118" s="130"/>
+      <c r="F118" s="44"/>
+      <c r="G118" s="159"/>
+      <c r="H118" s="128"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="140"/>
+      <c r="B119" s="129"/>
+      <c r="C119" s="140"/>
+      <c r="D119" s="157"/>
+      <c r="E119" s="155"/>
+      <c r="F119" s="157"/>
+      <c r="G119" s="160"/>
+      <c r="H119" s="128"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="141"/>
+      <c r="B120" s="141"/>
+      <c r="C120" s="141"/>
+      <c r="D120" s="128"/>
+      <c r="E120" s="128"/>
+      <c r="F120" s="128"/>
+      <c r="G120" s="128"/>
+      <c r="H120" s="128"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="141"/>
+      <c r="B121" s="141"/>
+      <c r="C121" s="141"/>
+      <c r="D121" s="156"/>
+      <c r="E121" s="153"/>
+      <c r="F121" s="156"/>
+      <c r="G121" s="158"/>
+      <c r="H121" s="128"/>
+    </row>
+    <row r="122" spans="1:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="A122" s="127"/>
+      <c r="B122" s="127"/>
+      <c r="C122" s="127"/>
+      <c r="D122" s="44"/>
+      <c r="E122" s="130"/>
+      <c r="F122" s="49"/>
+      <c r="G122" s="159"/>
+      <c r="H122" s="128"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="129"/>
+      <c r="B123" s="129"/>
+      <c r="C123" s="129"/>
+      <c r="D123" s="157"/>
+      <c r="E123" s="154"/>
+      <c r="F123" s="157"/>
+      <c r="G123" s="161"/>
+      <c r="H123" s="128"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="165"/>
+      <c r="B124" s="142"/>
+      <c r="C124" s="142"/>
+      <c r="D124" s="147"/>
+      <c r="E124" s="128"/>
+      <c r="F124" s="128"/>
+      <c r="G124" s="128"/>
+      <c r="H124" s="128"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="165"/>
+      <c r="B125" s="142"/>
+      <c r="C125" s="142"/>
+      <c r="D125" s="143"/>
+      <c r="E125" s="143"/>
+      <c r="F125" s="143"/>
+      <c r="G125" s="144"/>
+      <c r="H125" s="128"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="165"/>
+      <c r="B126" s="142"/>
+      <c r="C126" s="142"/>
+      <c r="D126" s="89"/>
+      <c r="E126" s="40"/>
+      <c r="F126" s="89"/>
+      <c r="G126" s="164"/>
+      <c r="H126" s="128"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="165"/>
+      <c r="B127" s="142"/>
+      <c r="C127" s="142"/>
+      <c r="D127" s="162"/>
+      <c r="E127" s="133"/>
+      <c r="F127" s="162"/>
+      <c r="G127" s="163"/>
+      <c r="H127" s="128"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="127"/>
+      <c r="B128" s="127"/>
+      <c r="C128" s="127"/>
+      <c r="D128" s="131"/>
+      <c r="E128" s="145"/>
+      <c r="F128" s="131"/>
+      <c r="G128" s="132"/>
+      <c r="H128" s="128"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="127"/>
+      <c r="B129" s="127"/>
+      <c r="C129" s="127"/>
+      <c r="D129" s="128"/>
+      <c r="E129" s="128"/>
+      <c r="F129" s="128"/>
+      <c r="G129" s="128"/>
+      <c r="H129" s="128"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="149"/>
+      <c r="B130" s="148"/>
+      <c r="C130" s="149"/>
+      <c r="D130" s="150"/>
+      <c r="E130" s="150"/>
+      <c r="F130" s="151"/>
+      <c r="G130" s="150"/>
+      <c r="H130" s="128"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="127"/>
+      <c r="B131" s="152"/>
+      <c r="C131" s="127"/>
+      <c r="D131" s="128"/>
+      <c r="E131" s="128"/>
+      <c r="F131" s="147"/>
+      <c r="G131" s="128"/>
+      <c r="H131" s="128"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" s="127"/>
+      <c r="B132" s="127"/>
+      <c r="C132" s="127"/>
+      <c r="D132" s="128"/>
+      <c r="E132" s="128"/>
+      <c r="F132" s="128"/>
+      <c r="G132" s="128"/>
+      <c r="H132" s="128"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="185"/>
+      <c r="B134" s="133"/>
+      <c r="C134" s="133"/>
+      <c r="D134" s="185"/>
+      <c r="E134" s="133"/>
+      <c r="F134" s="133"/>
+      <c r="G134" s="187"/>
+      <c r="H134" s="163"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="186"/>
+      <c r="B135" s="145"/>
+      <c r="C135" s="145"/>
+      <c r="D135" s="131"/>
+      <c r="E135" s="145"/>
+      <c r="F135" s="145"/>
+      <c r="G135" s="188"/>
+      <c r="H135" s="132"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="176"/>
+      <c r="B137" s="177"/>
+      <c r="C137" s="176"/>
+      <c r="D137" s="176"/>
+      <c r="E137" s="176"/>
+      <c r="F137" s="177"/>
+      <c r="G137" s="176"/>
+      <c r="H137" s="176"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>